--- a/data/spike.xlsx
+++ b/data/spike.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilpe\Documents\DOCUMENTS\ActuRank\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417063C9-46D9-49B5-B5B5-CB9B31D0F0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0BB654-F62F-4E85-9661-DE05A0418432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19155" yWindow="-21600" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="83">
   <si>
     <t>players</t>
   </si>
@@ -267,6 +267,24 @@
   </si>
   <si>
     <t>25/06/2026</t>
+  </si>
+  <si>
+    <t>22/07/2026</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Dave</t>
+  </si>
+  <si>
+    <t>7/07/2026</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
   </si>
 </sst>
 </file>
@@ -1747,9 +1765,15 @@
         <v/>
       </c>
       <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
@@ -10752,7 +10776,7 @@
       </c>
       <c r="J256" s="1"/>
       <c r="K256" s="9" t="str">
-        <f t="shared" ref="K256:K284" si="8">IF(OR(OR(AND(OR(A256=B256,A256=C256,A256=D256,B256=C256,B256=D256,C256=D256),OR(A256&lt;&gt;"",D256&lt;&gt;"")),H256&gt;MAX(F256:G256),B256=C256),OR(AND(ISBLANK(A256)=FALSE,ISNA(VLOOKUP(A256,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B256,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C256,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D256)=FALSE,ISNA(VLOOKUP(D256,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A256:D256)=1,COUNTBLANK(A256:D256)=3))),"ERREUR","")</f>
+        <f t="shared" ref="K256:K319" si="8">IF(OR(OR(AND(OR(A256=B256,A256=C256,A256=D256,B256=C256,B256=D256,C256=D256),OR(A256&lt;&gt;"",D256&lt;&gt;"")),H256&gt;MAX(F256:G256),B256=C256),OR(AND(ISBLANK(A256)=FALSE,ISNA(VLOOKUP(A256,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B256,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C256,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D256)=FALSE,ISNA(VLOOKUP(D256,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A256:D256)=1,COUNTBLANK(A256:D256)=3))),"ERREUR","")</f>
         <v/>
       </c>
       <c r="L256" s="1"/>
@@ -11125,6 +11149,7 @@
         <v>21</v>
       </c>
       <c r="E266" s="1">
+        <f t="shared" ref="E266:E336" si="9">IF(F266&gt;G266,1,0)</f>
         <v>1</v>
       </c>
       <c r="F266" s="5">
@@ -11163,6 +11188,7 @@
         <v>17</v>
       </c>
       <c r="E267" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F267" s="5">
@@ -11201,6 +11227,7 @@
         <v>17</v>
       </c>
       <c r="E268" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F268" s="5">
@@ -11239,6 +11266,7 @@
         <v>17</v>
       </c>
       <c r="E269" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F269" s="5">
@@ -11277,6 +11305,7 @@
         <v>11</v>
       </c>
       <c r="E270" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F270" s="5">
@@ -11315,6 +11344,7 @@
         <v>21</v>
       </c>
       <c r="E271" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F271" s="5">
@@ -11353,6 +11383,7 @@
         <v>17</v>
       </c>
       <c r="E272" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F272" s="5">
@@ -11391,6 +11422,7 @@
         <v>21</v>
       </c>
       <c r="E273" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F273" s="5">
@@ -11429,6 +11461,7 @@
         <v>21</v>
       </c>
       <c r="E274" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F274" s="5">
@@ -11467,6 +11500,7 @@
         <v>17</v>
       </c>
       <c r="E275" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F275" s="5">
@@ -11505,6 +11539,7 @@
         <v>11</v>
       </c>
       <c r="E276" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F276" s="5">
@@ -11543,6 +11578,7 @@
         <v>54</v>
       </c>
       <c r="E277" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F277" s="5">
@@ -11581,6 +11617,7 @@
         <v>54</v>
       </c>
       <c r="E278" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F278" s="5">
@@ -11619,6 +11656,7 @@
         <v>11</v>
       </c>
       <c r="E279" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F279" s="5">
@@ -11657,6 +11695,7 @@
         <v>54</v>
       </c>
       <c r="E280" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F280" s="5">
@@ -11695,6 +11734,7 @@
         <v>11</v>
       </c>
       <c r="E281" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F281" s="5">
@@ -11733,6 +11773,7 @@
         <v>21</v>
       </c>
       <c r="E282" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F282" s="5">
@@ -11771,6 +11812,7 @@
         <v>54</v>
       </c>
       <c r="E283" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F283" s="5">
@@ -11809,6 +11851,7 @@
         <v>11</v>
       </c>
       <c r="E284" s="1">
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F284" s="5">
@@ -11834,884 +11877,2028 @@
       <c r="O284" s="1"/>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A285" s="6"/>
-      <c r="B285" s="6"/>
-      <c r="C285" s="7"/>
-      <c r="D285" s="7"/>
-      <c r="E285" s="1"/>
-      <c r="F285" s="5"/>
-      <c r="G285" s="5"/>
-      <c r="H285" s="1"/>
-      <c r="I285" s="1"/>
+      <c r="A285" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E285" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F285" s="5">
+        <v>7</v>
+      </c>
+      <c r="G285" s="5">
+        <v>4</v>
+      </c>
+      <c r="H285" s="1">
+        <v>7</v>
+      </c>
+      <c r="I285" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J285" s="1"/>
-      <c r="K285" s="9"/>
+      <c r="K285" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L285" s="1"/>
       <c r="M285" s="1"/>
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A286" s="6"/>
-      <c r="B286" s="6"/>
-      <c r="C286" s="7"/>
-      <c r="D286" s="7"/>
-      <c r="E286" s="1"/>
-      <c r="F286" s="5"/>
-      <c r="G286" s="5"/>
-      <c r="H286" s="1"/>
-      <c r="I286" s="1"/>
+      <c r="A286" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D286" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E286" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F286" s="5">
+        <v>7</v>
+      </c>
+      <c r="G286" s="5">
+        <v>5</v>
+      </c>
+      <c r="H286" s="1">
+        <v>7</v>
+      </c>
+      <c r="I286" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J286" s="1"/>
-      <c r="K286" s="9"/>
+      <c r="K286" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L286" s="1"/>
       <c r="M286" s="1"/>
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A287" s="6"/>
-      <c r="B287" s="6"/>
-      <c r="C287" s="7"/>
-      <c r="D287" s="7"/>
-      <c r="E287" s="1"/>
-      <c r="F287" s="5"/>
-      <c r="G287" s="5"/>
-      <c r="H287" s="1"/>
-      <c r="I287" s="1"/>
+      <c r="A287" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E287" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F287" s="5">
+        <v>7</v>
+      </c>
+      <c r="G287" s="5">
+        <v>2</v>
+      </c>
+      <c r="H287" s="1">
+        <v>7</v>
+      </c>
+      <c r="I287" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J287" s="1"/>
-      <c r="K287" s="9"/>
+      <c r="K287" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L287" s="1"/>
       <c r="M287" s="1"/>
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A288" s="6"/>
-      <c r="B288" s="6"/>
-      <c r="C288" s="7"/>
-      <c r="D288" s="7"/>
-      <c r="E288" s="1"/>
-      <c r="F288" s="5"/>
-      <c r="G288" s="5"/>
-      <c r="H288" s="1"/>
-      <c r="I288" s="1"/>
+      <c r="A288" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E288" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F288" s="5">
+        <v>7</v>
+      </c>
+      <c r="G288" s="5">
+        <v>1</v>
+      </c>
+      <c r="H288" s="1">
+        <v>7</v>
+      </c>
+      <c r="I288" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J288" s="1"/>
-      <c r="K288" s="9"/>
+      <c r="K288" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L288" s="1"/>
       <c r="M288" s="1"/>
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A289" s="6"/>
-      <c r="B289" s="6"/>
-      <c r="C289" s="7"/>
-      <c r="D289" s="7"/>
-      <c r="E289" s="1"/>
-      <c r="F289" s="5"/>
-      <c r="G289" s="5"/>
-      <c r="H289" s="1"/>
-      <c r="I289" s="1"/>
+      <c r="A289" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E289" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F289" s="5">
+        <v>7</v>
+      </c>
+      <c r="G289" s="5">
+        <v>3</v>
+      </c>
+      <c r="H289" s="1">
+        <v>7</v>
+      </c>
+      <c r="I289" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J289" s="1"/>
-      <c r="K289" s="9"/>
+      <c r="K289" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L289" s="1"/>
       <c r="M289" s="1"/>
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A290" s="6"/>
-      <c r="B290" s="6"/>
-      <c r="C290" s="7"/>
-      <c r="D290" s="7"/>
-      <c r="E290" s="1"/>
-      <c r="F290" s="5"/>
-      <c r="G290" s="5"/>
-      <c r="H290" s="1"/>
-      <c r="I290" s="1"/>
+      <c r="A290" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E290" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F290" s="5">
+        <v>7</v>
+      </c>
+      <c r="G290" s="5">
+        <v>4</v>
+      </c>
+      <c r="H290" s="1">
+        <v>7</v>
+      </c>
+      <c r="I290" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J290" s="1"/>
-      <c r="K290" s="9"/>
+      <c r="K290" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L290" s="1"/>
       <c r="M290" s="1"/>
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A291" s="6"/>
-      <c r="B291" s="6"/>
-      <c r="C291" s="7"/>
-      <c r="D291" s="7"/>
-      <c r="E291" s="1"/>
-      <c r="F291" s="5"/>
-      <c r="G291" s="5"/>
-      <c r="H291" s="1"/>
-      <c r="I291" s="1"/>
+      <c r="A291" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E291" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F291" s="5">
+        <v>7</v>
+      </c>
+      <c r="G291" s="5">
+        <v>3</v>
+      </c>
+      <c r="H291" s="1">
+        <v>7</v>
+      </c>
+      <c r="I291" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J291" s="1"/>
-      <c r="K291" s="9"/>
+      <c r="K291" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L291" s="1"/>
       <c r="M291" s="1"/>
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A292" s="6"/>
-      <c r="B292" s="6"/>
-      <c r="C292" s="7"/>
-      <c r="D292" s="7"/>
-      <c r="E292" s="1"/>
-      <c r="F292" s="5"/>
-      <c r="G292" s="5"/>
-      <c r="H292" s="1"/>
-      <c r="I292" s="1"/>
+      <c r="A292" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D292" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E292" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F292" s="5">
+        <v>7</v>
+      </c>
+      <c r="G292" s="5">
+        <v>3</v>
+      </c>
+      <c r="H292" s="1">
+        <v>7</v>
+      </c>
+      <c r="I292" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J292" s="1"/>
-      <c r="K292" s="9"/>
+      <c r="K292" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L292" s="1"/>
       <c r="M292" s="1"/>
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A293" s="6"/>
-      <c r="B293" s="6"/>
-      <c r="C293" s="7"/>
-      <c r="D293" s="7"/>
-      <c r="E293" s="1"/>
-      <c r="F293" s="5"/>
-      <c r="G293" s="5"/>
-      <c r="H293" s="1"/>
-      <c r="I293" s="1"/>
+      <c r="A293" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E293" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F293" s="5">
+        <v>7</v>
+      </c>
+      <c r="G293" s="5">
+        <v>4</v>
+      </c>
+      <c r="H293" s="1">
+        <v>7</v>
+      </c>
+      <c r="I293" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J293" s="1"/>
-      <c r="K293" s="9"/>
+      <c r="K293" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L293" s="1"/>
       <c r="M293" s="1"/>
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A294" s="6"/>
-      <c r="B294" s="6"/>
-      <c r="C294" s="7"/>
-      <c r="D294" s="7"/>
-      <c r="E294" s="1"/>
-      <c r="F294" s="5"/>
-      <c r="G294" s="5"/>
-      <c r="H294" s="1"/>
-      <c r="I294" s="1"/>
+      <c r="A294" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E294" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F294" s="5">
+        <v>7</v>
+      </c>
+      <c r="G294" s="5">
+        <v>5</v>
+      </c>
+      <c r="H294" s="1">
+        <v>7</v>
+      </c>
+      <c r="I294" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J294" s="1"/>
-      <c r="K294" s="9"/>
+      <c r="K294" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L294" s="1"/>
       <c r="M294" s="1"/>
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A295" s="6"/>
-      <c r="B295" s="6"/>
-      <c r="C295" s="7"/>
-      <c r="D295" s="7"/>
-      <c r="E295" s="1"/>
-      <c r="F295" s="5"/>
-      <c r="G295" s="5"/>
-      <c r="H295" s="1"/>
-      <c r="I295" s="1"/>
+      <c r="A295" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E295" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F295" s="5">
+        <v>7</v>
+      </c>
+      <c r="G295" s="5">
+        <v>2</v>
+      </c>
+      <c r="H295" s="1">
+        <v>7</v>
+      </c>
+      <c r="I295" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J295" s="1"/>
-      <c r="K295" s="9"/>
+      <c r="K295" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L295" s="1"/>
       <c r="M295" s="1"/>
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A296" s="6"/>
-      <c r="B296" s="6"/>
-      <c r="C296" s="7"/>
-      <c r="D296" s="7"/>
-      <c r="E296" s="1"/>
-      <c r="F296" s="5"/>
-      <c r="G296" s="5"/>
-      <c r="H296" s="1"/>
-      <c r="I296" s="1"/>
+      <c r="A296" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E296" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F296" s="5">
+        <v>11</v>
+      </c>
+      <c r="G296" s="5">
+        <v>9</v>
+      </c>
+      <c r="H296" s="1">
+        <v>7</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J296" s="1"/>
-      <c r="K296" s="9"/>
+      <c r="K296" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L296" s="1"/>
       <c r="M296" s="1"/>
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A297" s="6"/>
-      <c r="B297" s="6"/>
-      <c r="C297" s="7"/>
-      <c r="D297" s="7"/>
-      <c r="E297" s="1"/>
-      <c r="F297" s="5"/>
-      <c r="G297" s="5"/>
-      <c r="H297" s="1"/>
-      <c r="I297" s="1"/>
+      <c r="A297" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E297" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F297" s="5">
+        <v>9</v>
+      </c>
+      <c r="G297" s="5">
+        <v>7</v>
+      </c>
+      <c r="H297" s="1">
+        <v>7</v>
+      </c>
+      <c r="I297" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J297" s="1"/>
-      <c r="K297" s="9"/>
+      <c r="K297" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L297" s="1"/>
       <c r="M297" s="1"/>
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A298" s="6"/>
-      <c r="B298" s="6"/>
-      <c r="C298" s="7"/>
-      <c r="D298" s="7"/>
-      <c r="E298" s="1"/>
-      <c r="F298" s="5"/>
-      <c r="G298" s="5"/>
-      <c r="H298" s="1"/>
-      <c r="I298" s="1"/>
+      <c r="A298" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D298" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E298" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F298" s="5">
+        <v>7</v>
+      </c>
+      <c r="G298" s="5">
+        <v>3</v>
+      </c>
+      <c r="H298" s="1">
+        <v>7</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J298" s="1"/>
-      <c r="K298" s="9"/>
+      <c r="K298" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L298" s="1"/>
       <c r="M298" s="1"/>
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A299" s="6"/>
-      <c r="B299" s="6"/>
-      <c r="C299" s="7"/>
-      <c r="D299" s="7"/>
-      <c r="E299" s="1"/>
-      <c r="F299" s="5"/>
-      <c r="G299" s="5"/>
-      <c r="H299" s="1"/>
-      <c r="I299" s="1"/>
+      <c r="A299" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D299" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E299" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F299" s="5">
+        <v>7</v>
+      </c>
+      <c r="G299" s="5">
+        <v>5</v>
+      </c>
+      <c r="H299" s="1">
+        <v>7</v>
+      </c>
+      <c r="I299" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="J299" s="1"/>
-      <c r="K299" s="9"/>
+      <c r="K299" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L299" s="1"/>
       <c r="M299" s="1"/>
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A300" s="6"/>
-      <c r="B300" s="6"/>
-      <c r="C300" s="7"/>
-      <c r="D300" s="7"/>
-      <c r="E300" s="1"/>
-      <c r="F300" s="5"/>
-      <c r="G300" s="5"/>
-      <c r="H300" s="1"/>
-      <c r="I300" s="1"/>
+      <c r="A300" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D300" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E300" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F300" s="5">
+        <v>12</v>
+      </c>
+      <c r="G300" s="5">
+        <v>10</v>
+      </c>
+      <c r="H300" s="1">
+        <v>11</v>
+      </c>
+      <c r="I300" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J300" s="1"/>
-      <c r="K300" s="9"/>
+      <c r="K300" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L300" s="1"/>
       <c r="M300" s="1"/>
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A301" s="6"/>
-      <c r="B301" s="6"/>
-      <c r="C301" s="7"/>
-      <c r="D301" s="7"/>
-      <c r="E301" s="1"/>
-      <c r="F301" s="5"/>
-      <c r="G301" s="5"/>
-      <c r="H301" s="1"/>
-      <c r="I301" s="1"/>
+      <c r="A301" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D301" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E301" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F301" s="5">
+        <v>7</v>
+      </c>
+      <c r="G301" s="5">
+        <v>4</v>
+      </c>
+      <c r="H301" s="1">
+        <v>7</v>
+      </c>
+      <c r="I301" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J301" s="1"/>
-      <c r="K301" s="9"/>
+      <c r="K301" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L301" s="1"/>
       <c r="M301" s="1"/>
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A302" s="6"/>
-      <c r="B302" s="6"/>
-      <c r="C302" s="7"/>
-      <c r="D302" s="7"/>
-      <c r="E302" s="1"/>
-      <c r="F302" s="5"/>
-      <c r="G302" s="5"/>
-      <c r="H302" s="1"/>
-      <c r="I302" s="1"/>
+      <c r="A302" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D302" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E302" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F302" s="5">
+        <v>7</v>
+      </c>
+      <c r="G302" s="5">
+        <v>0</v>
+      </c>
+      <c r="H302" s="1">
+        <v>7</v>
+      </c>
+      <c r="I302" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J302" s="1"/>
-      <c r="K302" s="9"/>
+      <c r="K302" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L302" s="1"/>
       <c r="M302" s="1"/>
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A303" s="6"/>
-      <c r="B303" s="6"/>
-      <c r="C303" s="7"/>
-      <c r="D303" s="7"/>
-      <c r="E303" s="1"/>
-      <c r="F303" s="5"/>
-      <c r="G303" s="5"/>
-      <c r="H303" s="1"/>
-      <c r="I303" s="1"/>
+      <c r="A303" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D303" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E303" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F303" s="5">
+        <v>7</v>
+      </c>
+      <c r="G303" s="5">
+        <v>1</v>
+      </c>
+      <c r="H303" s="1">
+        <v>7</v>
+      </c>
+      <c r="I303" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J303" s="1"/>
-      <c r="K303" s="9"/>
+      <c r="K303" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L303" s="1"/>
       <c r="M303" s="1"/>
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A304" s="6"/>
-      <c r="B304" s="6"/>
-      <c r="C304" s="7"/>
-      <c r="D304" s="7"/>
-      <c r="E304" s="1"/>
-      <c r="F304" s="5"/>
-      <c r="G304" s="5"/>
-      <c r="H304" s="1"/>
-      <c r="I304" s="1"/>
+      <c r="A304" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C304" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D304" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E304" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F304" s="5">
+        <v>7</v>
+      </c>
+      <c r="G304" s="5">
+        <v>4</v>
+      </c>
+      <c r="H304" s="1">
+        <v>7</v>
+      </c>
+      <c r="I304" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J304" s="1"/>
-      <c r="K304" s="9"/>
+      <c r="K304" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L304" s="1"/>
       <c r="M304" s="1"/>
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A305" s="6"/>
-      <c r="B305" s="6"/>
-      <c r="C305" s="7"/>
-      <c r="D305" s="7"/>
-      <c r="E305" s="1"/>
-      <c r="F305" s="5"/>
-      <c r="G305" s="5"/>
-      <c r="H305" s="1"/>
-      <c r="I305" s="1"/>
+      <c r="A305" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D305" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E305" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F305" s="5">
+        <v>7</v>
+      </c>
+      <c r="G305" s="5">
+        <v>0</v>
+      </c>
+      <c r="H305" s="1">
+        <v>7</v>
+      </c>
+      <c r="I305" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J305" s="1"/>
-      <c r="K305" s="9"/>
+      <c r="K305" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L305" s="1"/>
       <c r="M305" s="1"/>
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
     </row>
     <row r="306" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A306" s="6"/>
-      <c r="B306" s="6"/>
-      <c r="C306" s="7"/>
-      <c r="D306" s="7"/>
-      <c r="E306" s="1"/>
-      <c r="F306" s="5"/>
-      <c r="G306" s="5"/>
-      <c r="H306" s="1"/>
-      <c r="I306" s="1"/>
+      <c r="A306" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D306" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E306" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F306" s="5">
+        <v>7</v>
+      </c>
+      <c r="G306" s="5">
+        <v>4</v>
+      </c>
+      <c r="H306" s="1">
+        <v>7</v>
+      </c>
+      <c r="I306" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J306" s="1"/>
-      <c r="K306" s="9"/>
+      <c r="K306" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L306" s="1"/>
       <c r="M306" s="1"/>
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A307" s="6"/>
-      <c r="B307" s="6"/>
-      <c r="C307" s="7"/>
-      <c r="D307" s="7"/>
-      <c r="E307" s="1"/>
-      <c r="F307" s="5"/>
-      <c r="G307" s="5"/>
-      <c r="H307" s="1"/>
-      <c r="I307" s="1"/>
+      <c r="A307" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D307" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E307" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F307" s="5">
+        <v>8</v>
+      </c>
+      <c r="G307" s="5">
+        <v>6</v>
+      </c>
+      <c r="H307" s="1">
+        <v>7</v>
+      </c>
+      <c r="I307" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J307" s="1"/>
-      <c r="K307" s="9"/>
+      <c r="K307" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L307" s="1"/>
       <c r="M307" s="1"/>
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A308" s="6"/>
-      <c r="B308" s="6"/>
-      <c r="C308" s="7"/>
-      <c r="D308" s="7"/>
-      <c r="E308" s="1"/>
-      <c r="F308" s="5"/>
-      <c r="G308" s="5"/>
-      <c r="H308" s="1"/>
-      <c r="I308" s="1"/>
+      <c r="A308" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D308" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E308" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F308" s="5">
+        <v>7</v>
+      </c>
+      <c r="G308" s="5">
+        <v>1</v>
+      </c>
+      <c r="H308" s="1">
+        <v>7</v>
+      </c>
+      <c r="I308" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J308" s="1"/>
-      <c r="K308" s="9"/>
+      <c r="K308" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L308" s="1"/>
       <c r="M308" s="1"/>
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
     </row>
     <row r="309" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A309" s="6"/>
-      <c r="B309" s="6"/>
-      <c r="C309" s="7"/>
-      <c r="D309" s="7"/>
-      <c r="E309" s="1"/>
-      <c r="F309" s="5"/>
-      <c r="G309" s="5"/>
-      <c r="H309" s="1"/>
-      <c r="I309" s="1"/>
+      <c r="A309" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E309" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F309" s="5">
+        <v>7</v>
+      </c>
+      <c r="G309" s="5">
+        <v>5</v>
+      </c>
+      <c r="H309" s="1">
+        <v>7</v>
+      </c>
+      <c r="I309" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J309" s="1"/>
-      <c r="K309" s="9"/>
+      <c r="K309" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L309" s="1"/>
       <c r="M309" s="1"/>
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A310" s="6"/>
-      <c r="B310" s="6"/>
-      <c r="C310" s="7"/>
-      <c r="D310" s="7"/>
-      <c r="E310" s="1"/>
-      <c r="F310" s="5"/>
-      <c r="G310" s="5"/>
-      <c r="H310" s="1"/>
-      <c r="I310" s="1"/>
+      <c r="A310" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E310" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F310" s="5">
+        <v>7</v>
+      </c>
+      <c r="G310" s="5">
+        <v>5</v>
+      </c>
+      <c r="H310" s="1">
+        <v>7</v>
+      </c>
+      <c r="I310" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="J310" s="1"/>
-      <c r="K310" s="9"/>
+      <c r="K310" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L310" s="1"/>
       <c r="M310" s="1"/>
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A311" s="6"/>
-      <c r="B311" s="6"/>
-      <c r="C311" s="7"/>
-      <c r="D311" s="7"/>
-      <c r="E311" s="1"/>
-      <c r="F311" s="5"/>
-      <c r="G311" s="5"/>
-      <c r="H311" s="1"/>
-      <c r="I311" s="1"/>
+      <c r="A311" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E311" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F311" s="5">
+        <v>11</v>
+      </c>
+      <c r="G311" s="5">
+        <v>3</v>
+      </c>
+      <c r="H311" s="1">
+        <v>11</v>
+      </c>
+      <c r="I311" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J311" s="1"/>
-      <c r="K311" s="9"/>
+      <c r="K311" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L311" s="1"/>
       <c r="M311" s="1"/>
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
     </row>
     <row r="312" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A312" s="6"/>
-      <c r="B312" s="6"/>
-      <c r="C312" s="7"/>
-      <c r="D312" s="7"/>
-      <c r="E312" s="1"/>
-      <c r="F312" s="5"/>
-      <c r="G312" s="5"/>
-      <c r="H312" s="1"/>
-      <c r="I312" s="1"/>
+      <c r="A312" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D312" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E312" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F312" s="5">
+        <v>7</v>
+      </c>
+      <c r="G312" s="5">
+        <v>5</v>
+      </c>
+      <c r="H312" s="1">
+        <v>7</v>
+      </c>
+      <c r="I312" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J312" s="1"/>
-      <c r="K312" s="9"/>
+      <c r="K312" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L312" s="1"/>
       <c r="M312" s="1"/>
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A313" s="6"/>
-      <c r="B313" s="6"/>
-      <c r="C313" s="7"/>
-      <c r="D313" s="7"/>
-      <c r="E313" s="1"/>
-      <c r="F313" s="5"/>
-      <c r="G313" s="5"/>
-      <c r="H313" s="1"/>
-      <c r="I313" s="1"/>
+      <c r="A313" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C313" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D313" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E313" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F313" s="5">
+        <v>7</v>
+      </c>
+      <c r="G313" s="5">
+        <v>3</v>
+      </c>
+      <c r="H313" s="1">
+        <v>7</v>
+      </c>
+      <c r="I313" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J313" s="1"/>
-      <c r="K313" s="9"/>
+      <c r="K313" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L313" s="1"/>
       <c r="M313" s="1"/>
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A314" s="6"/>
-      <c r="B314" s="6"/>
-      <c r="C314" s="7"/>
-      <c r="D314" s="7"/>
-      <c r="E314" s="1"/>
-      <c r="F314" s="5"/>
-      <c r="G314" s="5"/>
-      <c r="H314" s="1"/>
-      <c r="I314" s="1"/>
+      <c r="A314" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C314" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D314" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E314" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F314" s="5">
+        <v>8</v>
+      </c>
+      <c r="G314" s="5">
+        <v>6</v>
+      </c>
+      <c r="H314" s="1">
+        <v>7</v>
+      </c>
+      <c r="I314" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J314" s="1"/>
-      <c r="K314" s="9"/>
+      <c r="K314" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L314" s="1"/>
       <c r="M314" s="1"/>
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A315" s="6"/>
-      <c r="B315" s="6"/>
-      <c r="C315" s="7"/>
-      <c r="D315" s="7"/>
-      <c r="E315" s="1"/>
-      <c r="F315" s="5"/>
-      <c r="G315" s="5"/>
-      <c r="H315" s="1"/>
-      <c r="I315" s="1"/>
+      <c r="A315" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C315" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D315" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E315" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F315" s="5">
+        <v>7</v>
+      </c>
+      <c r="G315" s="5">
+        <v>3</v>
+      </c>
+      <c r="H315" s="1">
+        <v>7</v>
+      </c>
+      <c r="I315" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J315" s="1"/>
-      <c r="K315" s="9"/>
+      <c r="K315" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L315" s="1"/>
       <c r="M315" s="1"/>
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A316" s="6"/>
-      <c r="B316" s="6"/>
-      <c r="C316" s="7"/>
-      <c r="D316" s="7"/>
-      <c r="E316" s="1"/>
-      <c r="F316" s="5"/>
-      <c r="G316" s="5"/>
-      <c r="H316" s="1"/>
-      <c r="I316" s="1"/>
+      <c r="A316" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C316" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D316" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E316" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F316" s="5">
+        <v>7</v>
+      </c>
+      <c r="G316" s="5">
+        <v>3</v>
+      </c>
+      <c r="H316" s="1">
+        <v>7</v>
+      </c>
+      <c r="I316" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J316" s="1"/>
-      <c r="K316" s="9"/>
+      <c r="K316" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L316" s="1"/>
       <c r="M316" s="1"/>
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
     </row>
     <row r="317" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A317" s="6"/>
-      <c r="B317" s="6"/>
-      <c r="C317" s="7"/>
-      <c r="D317" s="7"/>
-      <c r="E317" s="1"/>
-      <c r="F317" s="5"/>
-      <c r="G317" s="5"/>
-      <c r="H317" s="1"/>
-      <c r="I317" s="1"/>
+      <c r="A317" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C317" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D317" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E317" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F317" s="5">
+        <v>7</v>
+      </c>
+      <c r="G317" s="5">
+        <v>4</v>
+      </c>
+      <c r="H317" s="1">
+        <v>7</v>
+      </c>
+      <c r="I317" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J317" s="1"/>
-      <c r="K317" s="9"/>
+      <c r="K317" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L317" s="1"/>
       <c r="M317" s="1"/>
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
     </row>
     <row r="318" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A318" s="6"/>
-      <c r="B318" s="6"/>
-      <c r="C318" s="7"/>
-      <c r="D318" s="7"/>
-      <c r="E318" s="1"/>
-      <c r="F318" s="5"/>
-      <c r="G318" s="5"/>
-      <c r="H318" s="1"/>
-      <c r="I318" s="1"/>
+      <c r="A318" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C318" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D318" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E318" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F318" s="5">
+        <v>8</v>
+      </c>
+      <c r="G318" s="5">
+        <v>6</v>
+      </c>
+      <c r="H318" s="1">
+        <v>7</v>
+      </c>
+      <c r="I318" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J318" s="1"/>
-      <c r="K318" s="9"/>
+      <c r="K318" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L318" s="1"/>
       <c r="M318" s="1"/>
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A319" s="6"/>
-      <c r="B319" s="6"/>
-      <c r="C319" s="7"/>
-      <c r="D319" s="7"/>
-      <c r="E319" s="1"/>
-      <c r="F319" s="5"/>
-      <c r="G319" s="5"/>
-      <c r="H319" s="1"/>
-      <c r="I319" s="1"/>
+      <c r="A319" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C319" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D319" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E319" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F319" s="5">
+        <v>9</v>
+      </c>
+      <c r="G319" s="5">
+        <v>7</v>
+      </c>
+      <c r="H319" s="1">
+        <v>7</v>
+      </c>
+      <c r="I319" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J319" s="1"/>
-      <c r="K319" s="9"/>
+      <c r="K319" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L319" s="1"/>
       <c r="M319" s="1"/>
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
     </row>
     <row r="320" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A320" s="6"/>
-      <c r="B320" s="6"/>
-      <c r="C320" s="7"/>
-      <c r="D320" s="7"/>
-      <c r="E320" s="1"/>
-      <c r="F320" s="5"/>
-      <c r="G320" s="5"/>
-      <c r="H320" s="1"/>
-      <c r="I320" s="1"/>
+      <c r="A320" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C320" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E320" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F320" s="5">
+        <v>8</v>
+      </c>
+      <c r="G320" s="5">
+        <v>6</v>
+      </c>
+      <c r="H320" s="1">
+        <v>7</v>
+      </c>
+      <c r="I320" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J320" s="1"/>
-      <c r="K320" s="9"/>
+      <c r="K320" s="9" t="str">
+        <f t="shared" ref="K320:K336" si="10">IF(OR(OR(AND(OR(A320=B320,A320=C320,A320=D320,B320=C320,B320=D320,C320=D320),OR(A320&lt;&gt;"",D320&lt;&gt;"")),H320&gt;MAX(F320:G320),B320=C320),OR(AND(ISBLANK(A320)=FALSE,ISNA(VLOOKUP(A320,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B320,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C320,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D320)=FALSE,ISNA(VLOOKUP(D320,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A320:D320)=1,COUNTBLANK(A320:D320)=3))),"ERREUR","")</f>
+        <v/>
+      </c>
       <c r="L320" s="1"/>
       <c r="M320" s="1"/>
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A321" s="6"/>
-      <c r="B321" s="6"/>
-      <c r="C321" s="7"/>
-      <c r="D321" s="7"/>
-      <c r="E321" s="1"/>
-      <c r="F321" s="5"/>
-      <c r="G321" s="5"/>
-      <c r="H321" s="1"/>
-      <c r="I321" s="1"/>
+      <c r="A321" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C321" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D321" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E321" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F321" s="5">
+        <v>7</v>
+      </c>
+      <c r="G321" s="5">
+        <v>3</v>
+      </c>
+      <c r="H321" s="1">
+        <v>7</v>
+      </c>
+      <c r="I321" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J321" s="1"/>
-      <c r="K321" s="9"/>
+      <c r="K321" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L321" s="1"/>
       <c r="M321" s="1"/>
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A322" s="6"/>
-      <c r="B322" s="6"/>
-      <c r="C322" s="7"/>
-      <c r="D322" s="7"/>
-      <c r="E322" s="1"/>
-      <c r="F322" s="5"/>
-      <c r="G322" s="5"/>
-      <c r="H322" s="1"/>
-      <c r="I322" s="1"/>
+      <c r="A322" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C322" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D322" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E322" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F322" s="5">
+        <v>7</v>
+      </c>
+      <c r="G322" s="5">
+        <v>5</v>
+      </c>
+      <c r="H322" s="1">
+        <v>7</v>
+      </c>
+      <c r="I322" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J322" s="1"/>
-      <c r="K322" s="9"/>
+      <c r="K322" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L322" s="1"/>
       <c r="M322" s="1"/>
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A323" s="6"/>
-      <c r="B323" s="6"/>
-      <c r="C323" s="7"/>
-      <c r="D323" s="7"/>
-      <c r="E323" s="1"/>
-      <c r="F323" s="5"/>
-      <c r="G323" s="5"/>
-      <c r="H323" s="1"/>
-      <c r="I323" s="1"/>
+      <c r="A323" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C323" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D323" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E323" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F323" s="5">
+        <v>7</v>
+      </c>
+      <c r="G323" s="5">
+        <v>5</v>
+      </c>
+      <c r="H323" s="1">
+        <v>7</v>
+      </c>
+      <c r="I323" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="J323" s="1"/>
-      <c r="K323" s="9"/>
+      <c r="K323" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L323" s="1"/>
       <c r="M323" s="1"/>
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
     </row>
     <row r="324" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A324" s="6"/>
-      <c r="B324" s="6"/>
-      <c r="C324" s="7"/>
-      <c r="D324" s="7"/>
-      <c r="E324" s="1"/>
-      <c r="F324" s="5"/>
-      <c r="G324" s="5"/>
-      <c r="H324" s="1"/>
-      <c r="I324" s="1"/>
+      <c r="A324" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C324" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D324" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E324" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F324" s="5">
+        <v>7</v>
+      </c>
+      <c r="G324" s="5">
+        <v>0</v>
+      </c>
+      <c r="H324" s="1">
+        <v>7</v>
+      </c>
+      <c r="I324" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J324" s="1"/>
-      <c r="K324" s="9"/>
+      <c r="K324" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L324" s="1"/>
       <c r="M324" s="1"/>
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A325" s="6"/>
-      <c r="B325" s="6"/>
-      <c r="C325" s="7"/>
-      <c r="D325" s="7"/>
-      <c r="E325" s="1"/>
-      <c r="F325" s="5"/>
-      <c r="G325" s="5"/>
-      <c r="H325" s="1"/>
-      <c r="I325" s="1"/>
+      <c r="A325" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C325" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D325" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E325" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F325" s="5">
+        <v>7</v>
+      </c>
+      <c r="G325" s="5">
+        <v>4</v>
+      </c>
+      <c r="H325" s="1">
+        <v>7</v>
+      </c>
+      <c r="I325" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J325" s="1"/>
-      <c r="K325" s="9"/>
+      <c r="K325" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L325" s="1"/>
       <c r="M325" s="1"/>
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A326" s="6"/>
-      <c r="B326" s="6"/>
-      <c r="C326" s="7"/>
-      <c r="D326" s="7"/>
-      <c r="E326" s="1"/>
-      <c r="F326" s="5"/>
-      <c r="G326" s="5"/>
-      <c r="H326" s="1"/>
-      <c r="I326" s="1"/>
+      <c r="A326" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C326" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E326" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F326" s="5">
+        <v>7</v>
+      </c>
+      <c r="G326" s="5">
+        <v>2</v>
+      </c>
+      <c r="H326" s="1">
+        <v>7</v>
+      </c>
+      <c r="I326" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J326" s="1"/>
-      <c r="K326" s="9"/>
+      <c r="K326" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L326" s="1"/>
       <c r="M326" s="1"/>
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A327" s="6"/>
-      <c r="B327" s="6"/>
-      <c r="C327" s="7"/>
-      <c r="D327" s="7"/>
-      <c r="E327" s="1"/>
-      <c r="F327" s="5"/>
-      <c r="G327" s="5"/>
-      <c r="H327" s="1"/>
-      <c r="I327" s="1"/>
+      <c r="A327" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C327" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D327" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E327" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F327" s="5">
+        <v>7</v>
+      </c>
+      <c r="G327" s="5">
+        <v>2</v>
+      </c>
+      <c r="H327" s="1">
+        <v>7</v>
+      </c>
+      <c r="I327" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J327" s="1"/>
-      <c r="K327" s="9"/>
+      <c r="K327" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L327" s="1"/>
       <c r="M327" s="1"/>
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A328" s="6"/>
-      <c r="B328" s="6"/>
-      <c r="C328" s="7"/>
-      <c r="D328" s="7"/>
-      <c r="E328" s="1"/>
-      <c r="F328" s="5"/>
-      <c r="G328" s="5"/>
-      <c r="H328" s="1"/>
-      <c r="I328" s="1"/>
+      <c r="A328" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C328" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D328" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E328" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F328" s="5">
+        <v>7</v>
+      </c>
+      <c r="G328" s="5">
+        <v>5</v>
+      </c>
+      <c r="H328" s="1">
+        <v>7</v>
+      </c>
+      <c r="I328" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J328" s="1"/>
-      <c r="K328" s="9"/>
+      <c r="K328" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L328" s="1"/>
       <c r="M328" s="1"/>
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A329" s="6"/>
-      <c r="B329" s="6"/>
-      <c r="C329" s="7"/>
-      <c r="D329" s="7"/>
-      <c r="E329" s="1"/>
-      <c r="F329" s="5"/>
-      <c r="G329" s="5"/>
-      <c r="H329" s="1"/>
-      <c r="I329" s="1"/>
+      <c r="A329" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C329" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D329" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E329" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F329" s="5">
+        <v>7</v>
+      </c>
+      <c r="G329" s="5">
+        <v>4</v>
+      </c>
+      <c r="H329" s="1">
+        <v>7</v>
+      </c>
+      <c r="I329" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J329" s="1"/>
-      <c r="K329" s="9"/>
+      <c r="K329" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L329" s="1"/>
       <c r="M329" s="1"/>
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A330" s="6"/>
-      <c r="B330" s="6"/>
-      <c r="C330" s="7"/>
-      <c r="D330" s="7"/>
-      <c r="E330" s="1"/>
-      <c r="F330" s="5"/>
-      <c r="G330" s="5"/>
-      <c r="H330" s="1"/>
-      <c r="I330" s="1"/>
+      <c r="A330" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C330" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D330" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E330" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F330" s="5">
+        <v>7</v>
+      </c>
+      <c r="G330" s="5">
+        <v>5</v>
+      </c>
+      <c r="H330" s="1">
+        <v>7</v>
+      </c>
+      <c r="I330" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J330" s="1"/>
-      <c r="K330" s="9"/>
+      <c r="K330" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L330" s="1"/>
       <c r="M330" s="1"/>
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A331" s="6"/>
-      <c r="B331" s="6"/>
-      <c r="C331" s="7"/>
-      <c r="D331" s="7"/>
-      <c r="E331" s="1"/>
-      <c r="F331" s="5"/>
-      <c r="G331" s="5"/>
-      <c r="H331" s="1"/>
-      <c r="I331" s="1"/>
+      <c r="A331" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C331" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D331" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E331" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F331" s="5">
+        <v>10</v>
+      </c>
+      <c r="G331" s="5">
+        <v>8</v>
+      </c>
+      <c r="H331" s="1">
+        <v>7</v>
+      </c>
+      <c r="I331" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J331" s="1"/>
-      <c r="K331" s="9"/>
+      <c r="K331" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L331" s="1"/>
       <c r="M331" s="1"/>
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A332" s="6"/>
-      <c r="B332" s="6"/>
-      <c r="C332" s="7"/>
-      <c r="D332" s="7"/>
-      <c r="E332" s="1"/>
-      <c r="F332" s="5"/>
-      <c r="G332" s="5"/>
-      <c r="H332" s="1"/>
-      <c r="I332" s="1"/>
+      <c r="A332" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C332" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D332" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E332" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F332" s="5">
+        <v>7</v>
+      </c>
+      <c r="G332" s="5">
+        <v>2</v>
+      </c>
+      <c r="H332" s="1">
+        <v>7</v>
+      </c>
+      <c r="I332" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J332" s="1"/>
-      <c r="K332" s="9"/>
+      <c r="K332" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L332" s="1"/>
       <c r="M332" s="1"/>
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A333" s="6"/>
-      <c r="B333" s="6"/>
-      <c r="C333" s="7"/>
-      <c r="D333" s="7"/>
-      <c r="E333" s="1"/>
-      <c r="F333" s="5"/>
-      <c r="G333" s="5"/>
-      <c r="H333" s="1"/>
-      <c r="I333" s="1"/>
+      <c r="A333" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C333" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D333" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E333" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F333" s="5">
+        <v>7</v>
+      </c>
+      <c r="G333" s="5">
+        <v>5</v>
+      </c>
+      <c r="H333" s="1">
+        <v>7</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J333" s="1"/>
-      <c r="K333" s="9"/>
+      <c r="K333" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L333" s="1"/>
       <c r="M333" s="1"/>
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A334" s="6"/>
-      <c r="B334" s="6"/>
-      <c r="C334" s="7"/>
-      <c r="D334" s="7"/>
-      <c r="E334" s="1"/>
-      <c r="F334" s="5"/>
-      <c r="G334" s="5"/>
-      <c r="H334" s="1"/>
-      <c r="I334" s="1"/>
+      <c r="A334" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C334" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D334" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E334" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F334" s="5">
+        <v>7</v>
+      </c>
+      <c r="G334" s="5">
+        <v>5</v>
+      </c>
+      <c r="H334" s="1">
+        <v>7</v>
+      </c>
+      <c r="I334" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J334" s="1"/>
-      <c r="K334" s="9"/>
+      <c r="K334" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L334" s="1"/>
       <c r="M334" s="1"/>
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A335" s="6"/>
-      <c r="B335" s="6"/>
-      <c r="C335" s="7"/>
-      <c r="D335" s="7"/>
-      <c r="E335" s="1"/>
-      <c r="F335" s="5"/>
-      <c r="G335" s="5"/>
-      <c r="H335" s="1"/>
-      <c r="I335" s="1"/>
+      <c r="A335" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C335" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E335" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F335" s="5">
+        <v>7</v>
+      </c>
+      <c r="G335" s="5">
+        <v>4</v>
+      </c>
+      <c r="H335" s="1">
+        <v>7</v>
+      </c>
+      <c r="I335" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J335" s="1"/>
-      <c r="K335" s="9"/>
+      <c r="K335" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L335" s="1"/>
       <c r="M335" s="1"/>
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
     </row>
     <row r="336" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A336" s="6"/>
-      <c r="B336" s="6"/>
-      <c r="C336" s="7"/>
-      <c r="D336" s="7"/>
-      <c r="E336" s="1"/>
-      <c r="F336" s="5"/>
-      <c r="G336" s="5"/>
-      <c r="H336" s="1"/>
-      <c r="I336" s="1"/>
+      <c r="A336" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C336" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E336" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="F336" s="5">
+        <v>23</v>
+      </c>
+      <c r="G336" s="5">
+        <v>21</v>
+      </c>
+      <c r="H336" s="1">
+        <v>21</v>
+      </c>
+      <c r="I336" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="J336" s="1"/>
-      <c r="K336" s="9"/>
+      <c r="K336" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="L336" s="1"/>
       <c r="M336" s="1"/>
       <c r="N336" s="1"/>
